--- a/data/raw/individual/ID 002/continuous/mHLEA_excel/TUM_S002_mHLEA_excel_20250716.xlsx
+++ b/data/raw/individual/ID 002/continuous/mHLEA_excel/TUM_S002_mHLEA_excel_20250716.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarina/LRZ Sync+Share/Light Logger Study Data/raw/individual/ID 002/continuous/mHLEA_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/HildenEtAl_Dataset_2025/data/raw/individual/ID 002/continuous/mHLEA_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48A4F4A7-D25C-3047-94ED-4BC425D09EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D25918-D727-2C48-8132-0A843C6EF7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="500" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
+    <workbookView xWindow="1160" yWindow="780" windowWidth="29240" windowHeight="18980" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">I </t>
   </si>
   <si>
-    <t>8: Sports indoors</t>
+    <t>I+L+E</t>
   </si>
   <si>
-    <t>I+L+E</t>
+    <t>Sports indoors</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>45441.624999999847</v>
@@ -1226,7 +1226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <f t="shared" si="0"/>
         <v>45441.666666666511</v>
@@ -1238,7 +1238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <f t="shared" si="0"/>
         <v>45441.708333333176</v>
@@ -1246,11 +1246,14 @@
       <c r="B67" t="s">
         <v>11</v>
       </c>
-      <c r="C67" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C67">
+        <v>8</v>
+      </c>
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <f t="shared" ref="A68:A131" si="1">A67 + TIME(1, 0, 0)</f>
         <v>45441.74999999984</v>
@@ -1262,7 +1265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <f t="shared" si="1"/>
         <v>45441.791666666504</v>
@@ -1274,7 +1277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <f t="shared" si="1"/>
         <v>45441.833333333168</v>
@@ -1286,7 +1289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <f t="shared" si="1"/>
         <v>45441.874999999833</v>
@@ -1298,7 +1301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <f t="shared" si="1"/>
         <v>45441.916666666497</v>
@@ -1310,7 +1313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <f t="shared" si="1"/>
         <v>45441.958333333161</v>
@@ -1322,7 +1325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <f t="shared" si="1"/>
         <v>45441.999999999825</v>
@@ -1334,7 +1337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <f t="shared" si="1"/>
         <v>45442.04166666649</v>
@@ -1346,7 +1349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <f t="shared" si="1"/>
         <v>45442.083333333154</v>
@@ -1358,7 +1361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <f t="shared" si="1"/>
         <v>45442.124999999818</v>
@@ -1370,7 +1373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <f t="shared" si="1"/>
         <v>45442.166666666482</v>
@@ -1382,7 +1385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <f t="shared" si="1"/>
         <v>45442.208333333147</v>
@@ -1394,7 +1397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <f t="shared" si="1"/>
         <v>45442.249999999811</v>
@@ -1436,7 +1439,7 @@
         <v>45442.374999999804</v>
       </c>
       <c r="B83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C83">
         <v>5</v>
@@ -1448,7 +1451,7 @@
         <v>45442.416666666468</v>
       </c>
       <c r="B84" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C84">
         <v>5</v>
@@ -1460,7 +1463,7 @@
         <v>45442.458333333132</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C85">
         <v>5</v>
